--- a/Sedes_a_priorizar_NasaUus.xlsx
+++ b/Sedes_a_priorizar_NasaUus.xlsx
@@ -497,11 +497,11 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SOTARA</t>
+          <t>POPAYAN</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>63.34754181034482</v>
+        <v>63.37491034482758</v>
       </c>
     </row>
     <row r="4">
